--- a/data/scholar-journal.xlsx
+++ b/data/scholar-journal.xlsx
@@ -1,50 +1,295 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LLA\Documents\Angel Leus\database\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CA5441-EDB5-4222-AC43-4C451B16DA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Roster" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
+  <si>
+    <t>Household ID</t>
+  </si>
+  <si>
+    <t>Scholar</t>
+  </si>
+  <si>
+    <t>Academic</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>HH-001</t>
+  </si>
+  <si>
+    <t>MATEO ASUMEN BOBILES</t>
+  </si>
+  <si>
+    <t>HH-002</t>
+  </si>
+  <si>
+    <t>JUNRISH EBUENGA CAONES</t>
+  </si>
+  <si>
+    <t>HH-003</t>
+  </si>
+  <si>
+    <t>RICHLYN LANDICHO CAPULO</t>
+  </si>
+  <si>
+    <t>HH-004</t>
+  </si>
+  <si>
+    <t>FRANCIS ALLESANDRO CASPE CUSTODIO</t>
+  </si>
+  <si>
+    <t>ALFRED LUIZ CASPE CUSTODIO</t>
+  </si>
+  <si>
+    <t>HH-005</t>
+  </si>
+  <si>
+    <t>REYNIEL ALLEN ROBLES ESCUETA</t>
+  </si>
+  <si>
+    <t>BRIAN ANNIEL ROBLES ESCUETA</t>
+  </si>
+  <si>
+    <t>HH-006</t>
+  </si>
+  <si>
+    <t>JOHN CARLO BARRUGA LAZANAS</t>
+  </si>
+  <si>
+    <t>HH-007</t>
+  </si>
+  <si>
+    <t>PHILIP ANDREW CABALLERO LOGRONIO</t>
+  </si>
+  <si>
+    <t>HH-008</t>
+  </si>
+  <si>
+    <t>CANDICE BARLOLAY MOSQUERA</t>
+  </si>
+  <si>
+    <t>VINICE BARTOLAY MOSQUERA</t>
+  </si>
+  <si>
+    <t>HH-009</t>
+  </si>
+  <si>
+    <t>RHEAN MARK MAGANA PACHECO</t>
+  </si>
+  <si>
+    <t>HH-010</t>
+  </si>
+  <si>
+    <t>AKEESHA LIANNE ALCAZAR ROSALES</t>
+  </si>
+  <si>
+    <t>HH-011</t>
+  </si>
+  <si>
+    <t>JOSHUA DAVID RELLATORRES ROSAS</t>
+  </si>
+  <si>
+    <t>HH-012</t>
+  </si>
+  <si>
+    <t>VINCE ARON SANGALANG SUGUITAN</t>
+  </si>
+  <si>
+    <t>HH-013</t>
+  </si>
+  <si>
+    <t>TRICIA YHANIE ABITO BIEN</t>
+  </si>
+  <si>
+    <t>HH-014</t>
+  </si>
+  <si>
+    <t>KRIZZEL CADE AUSTRIA DERLA</t>
+  </si>
+  <si>
+    <t>HH-015</t>
+  </si>
+  <si>
+    <t>HERSHEY MHAORI HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HH-016</t>
+  </si>
+  <si>
+    <t>RHAYNE LUMAG MARTINEZ</t>
+  </si>
+  <si>
+    <t>HH-017</t>
+  </si>
+  <si>
+    <t>KEISHA BRICE PANOPIO MELEGRITO</t>
+  </si>
+  <si>
+    <t>KAILENE SHANE PANOPIO MELEGRITO</t>
+  </si>
+  <si>
+    <t>HH-018</t>
+  </si>
+  <si>
+    <t>KYLE BRENAN SAGADRACA MENDOZA</t>
+  </si>
+  <si>
+    <t>HH-019</t>
+  </si>
+  <si>
+    <t>NICOLE ANNE UROT SABAL</t>
+  </si>
+  <si>
+    <t>HH-020</t>
+  </si>
+  <si>
+    <t>AIKEE MIKAELA MIRANDUQUE SANTOS</t>
+  </si>
+  <si>
+    <t>HH-021</t>
+  </si>
+  <si>
+    <t>QUIM DRIZEL QUIMIO TOLENTINO</t>
+  </si>
+  <si>
+    <t>HH-022</t>
+  </si>
+  <si>
+    <t>XYRA HYACINTH RODRIGUEZ CLEOPAS</t>
+  </si>
+  <si>
+    <t>HH-023</t>
+  </si>
+  <si>
+    <t>SAMANTHA RAGODON ECRAELA</t>
+  </si>
+  <si>
+    <t>HH-024</t>
+  </si>
+  <si>
+    <t>FAITH EUNICE FAMILIAR FLORES</t>
+  </si>
+  <si>
+    <t>HH-025</t>
+  </si>
+  <si>
+    <t>ERIC JOSH SANTIAGO GARCIA</t>
+  </si>
+  <si>
+    <t>HH-026</t>
+  </si>
+  <si>
+    <t>ANGELU T. NUMERON</t>
+  </si>
+  <si>
+    <t>HH-027</t>
+  </si>
+  <si>
+    <t>NASH IVAN RAFALLO PANTOJA</t>
+  </si>
+  <si>
+    <t>HH-028</t>
+  </si>
+  <si>
+    <t>ALLYN BAUTISTA RONDINA</t>
+  </si>
+  <si>
+    <t>HH-029</t>
+  </si>
+  <si>
+    <t>HANNA KIMBERLIE VALERA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>HH-030</t>
+  </si>
+  <si>
+    <t>ANYA NATALIE HERNANDEZ DETRUZ</t>
+  </si>
+  <si>
+    <t>HH-031</t>
+  </si>
+  <si>
+    <t>RHAINE JANNELLE SUA NACIONALES</t>
+  </si>
+  <si>
+    <t>HH-032</t>
+  </si>
+  <si>
+    <t>ANDREA NICOLE PAR MERCADO</t>
+  </si>
+  <si>
+    <t>HH-033</t>
+  </si>
+  <si>
+    <t>GRACE ANUYO UMALI</t>
+  </si>
+  <si>
+    <t>HH-034</t>
+  </si>
+  <si>
+    <t>EUSSEY AOE SAN JUAN DEINLA</t>
+  </si>
+  <si>
+    <t>HH-035</t>
+  </si>
+  <si>
+    <t>ARVEL NICOLE TERCERO UMALI</t>
+  </si>
+  <si>
+    <t>HH-036</t>
+  </si>
+  <si>
+    <t>FRANCHESCA LUBANG SISCON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parental </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,85 +304,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -216,6 +398,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,6 +433,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -284,20 +468,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -419,148 +599,1007 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="15.796875" customWidth="1"/>
+    <col min="2" max="2" width="40.796875" customWidth="1"/>
+    <col min="3" max="7" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Household ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Scholar</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Academic</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Parental</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HH-000</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>[SAMPLE STUDENT]</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HH-000</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>[SAMPLE SIBLING]</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HH-001</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>[SAMPLE SCHOLAR]</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>10</v>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A2:G41 A1:F1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>